--- a/data/trans_dic/P64D$otros_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,15</t>
+          <t>0,22; 3,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,16</t>
+          <t>0,22; 1,93</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,26</t>
+          <t>0,29; 2,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,6</t>
+          <t>0,29; 1,54</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,08</t>
+          <t>0,21; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,77</t>
+          <t>0,31; 1,91</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,44</t>
+          <t>0,07; 1,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,35</t>
+          <t>0,26; 2,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,44</t>
+          <t>0,3; 1,45</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,4</t>
+          <t>0,42; 1,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,16</t>
+          <t>0,31; 1,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,1</t>
+          <t>0,49; 1,11</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>731; 10499</t>
+          <t>738; 11564</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3245</t>
+          <t>0; 3636</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1280; 12789</t>
+          <t>1276; 11409</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1998; 18239</t>
+          <t>2319; 17687</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5856</t>
+          <t>0; 5819</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3625; 19355</t>
+          <t>3512; 18583</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7862</t>
+          <t>0; 7715</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>699; 9942</t>
+          <t>671; 9007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1553; 11985</t>
+          <t>2080; 12958</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>325; 6767</t>
+          <t>331; 6940</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1377; 11279</t>
+          <t>1260; 11275</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2718; 13668</t>
+          <t>2859; 13812</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8230; 27537</t>
+          <t>8286; 27774</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4348; 16983</t>
+          <t>4559; 16711</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15689; 37855</t>
+          <t>16684; 38207</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$otros_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,47</t>
+          <t>0,2; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,93</t>
+          <t>0,2; 2,05</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,2</t>
+          <t>0,89; 3,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,54</t>
+          <t>0,58; 1,99</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,79</t>
+          <t>0,4; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,91</t>
+          <t>0,29; 1,63</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,47</t>
+          <t>0,22; 2,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,35</t>
+          <t>0,65; 3,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,45</t>
+          <t>0,64; 2,4</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,41</t>
+          <t>0,7; 1,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,14</t>
+          <t>0,47; 1,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,11</t>
+          <t>0,67; 1,42</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>634</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4481</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>738; 11564</t>
+          <t>723; 11620</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3636</t>
+          <t>0; 3180</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1276; 11409</t>
+          <t>1291; 13217</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>12119</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2319; 17687</t>
+          <t>5587; 20324</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5819</t>
+          <t>0; 5587</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3512; 18583</t>
+          <t>6262; 21443</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5887</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7715</t>
+          <t>0; 7519</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>671; 9007</t>
+          <t>1364; 10524</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2080; 12958</t>
+          <t>2182; 12295</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>11897</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>331; 6940</t>
+          <t>1119; 10674</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1260; 11275</t>
+          <t>2919; 17147</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2859; 13812</t>
+          <t>6140; 23118</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8286; 27774</t>
+          <t>13532; 33169</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4559; 16711</t>
+          <t>7113; 24994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16684; 38207</t>
+          <t>23200; 48742</t>
         </is>
       </c>
     </row>
